--- a/data/trans_orig/P1435-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1435-Clase-trans_orig.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,25 +526,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de dolor menstrual en 2007</t>
+          <t>Población con diagnóstico de dolor menstrual en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +548,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -564,17 +557,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -645,41 +627,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -702,13 +649,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -723,37 +663,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21969</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14384</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>32019</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13922</t>
+          <t>14384</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32898</t>
+          <t>32019</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,47 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>21969</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>13922</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>32898</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>7,16%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>4,54%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>10,73%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -836,37 +741,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>276</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>284711</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>274661</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>292296</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>273782</t>
+          <t>274661</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>292758</t>
+          <t>292296</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,47 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>284711</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>273782</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>292758</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>92,84%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>89,27%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>95,46%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -949,37 +819,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>298</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>306680</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>306680</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>306680</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1013,41 +883,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>298</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>306680</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>306680</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>306680</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1066,37 +901,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>50375</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>38199</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>63879</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +946,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38430</t>
+          <t>38199</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64737</t>
+          <t>63879</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,47 +961,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>50375</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>38430</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>64737</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>13,55%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>10,33%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>17,41%</t>
+          <t>17,18%</t>
         </is>
       </c>
     </row>
@@ -1179,37 +979,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>314</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>321490</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>307986</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>333666</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1024,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>307128</t>
+          <t>307986</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>333435</t>
+          <t>333666</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,47 +1039,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>321490</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>307128</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>333435</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>86,45%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>82,59%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>89,67%</t>
+          <t>89,73%</t>
         </is>
       </c>
     </row>
@@ -1292,37 +1057,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>363</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>371865</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>371865</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>371865</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1356,41 +1121,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>363</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>371865</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>371865</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>371865</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1409,37 +1139,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15669</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9266</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>25028</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1184,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9115</t>
+          <t>9266</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24274</t>
+          <t>25028</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,47 +1199,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>15669</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>9115</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>24274</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>9,34%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>5,43%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>14,47%</t>
+          <t>14,92%</t>
         </is>
       </c>
     </row>
@@ -1522,37 +1217,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>149</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>152113</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>142754</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>158516</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1262,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>143508</t>
+          <t>142754</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158667</t>
+          <t>158516</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,47 +1277,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>152113</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>143508</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>158667</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>90,66%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>85,53%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>94,57%</t>
+          <t>94,48%</t>
         </is>
       </c>
     </row>
@@ -1635,37 +1295,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>164</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>167782</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>167782</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>167782</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1699,41 +1359,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>167782</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>167782</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>167782</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1752,37 +1377,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>69057</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>54519</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>85252</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1422,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53775</t>
+          <t>54519</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84806</t>
+          <t>85252</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,47 +1437,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>69057</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>53775</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>84806</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>9,67%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>7,53%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>11,87%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -1865,37 +1455,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>624</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>645228</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>629033</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>659766</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>629479</t>
+          <t>629033</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>660510</t>
+          <t>659766</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,47 +1515,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>645228</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>629479</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>660510</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>90,33%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>88,13%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>92,47%</t>
+          <t>92,37%</t>
         </is>
       </c>
     </row>
@@ -1978,37 +1533,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>694</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>714285</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>714285</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>714285</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2042,41 +1597,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>694</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>714285</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>714285</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>714285</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2095,37 +1615,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>27599</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18567</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>39060</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +1660,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17951</t>
+          <t>18567</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39125</t>
+          <t>39060</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,47 +1675,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>27599</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>17951</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>39125</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>4,85%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>6,88%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -2208,37 +1693,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>514</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>541153</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>529692</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>550185</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +1738,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>529627</t>
+          <t>529692</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>550801</t>
+          <t>550185</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,47 +1753,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>514</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>541153</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>529627</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>550801</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>95,15%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>93,12%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>96,84%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -2321,37 +1771,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>539</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>568752</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>568752</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>568752</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2385,41 +1835,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>539</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>568752</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>568752</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>568752</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2438,37 +1853,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>75476</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>62330</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>93823</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +1898,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>60600</t>
+          <t>62330</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>95356</t>
+          <t>93823</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,47 +1913,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>75476</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>60600</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>95356</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>6,04%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>4,85%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>7,64%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -2551,37 +1931,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1173284</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1154937</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1186430</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +1976,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1153404</t>
+          <t>1154937</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1188160</t>
+          <t>1186430</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,47 +1991,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1160</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1173284</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>1153404</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>1188160</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>93,96%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>92,36%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>95,15%</t>
+          <t>95,01%</t>
         </is>
       </c>
     </row>
@@ -2664,37 +2009,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1248760</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1248760</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1248760</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2728,41 +2073,6 @@
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>1238</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>1248760</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>1248760</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>1248760</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2781,37 +2091,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>259</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>260146</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>234102</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>292170</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2136,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>228846</t>
+          <t>234102</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>291870</t>
+          <t>292170</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,47 +2151,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>260146</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>228846</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>291870</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>7,7%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>6,77%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -2894,37 +2169,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3117978</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3085954</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3144022</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2214,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3086254</t>
+          <t>3085954</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3149278</t>
+          <t>3144022</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,47 +2229,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>3117978</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>3086254</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>3149278</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>92,3%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>91,36%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>93,23%</t>
+          <t>93,07%</t>
         </is>
       </c>
     </row>
@@ -3007,37 +2247,37 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3296</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3378124</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3378124</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3378124</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3071,41 +2311,6 @@
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>3296</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>3378124</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>3378124</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>3378124</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3119,7 +2324,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -3127,7 +2332,6 @@
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
@@ -3142,7 +2346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3161,25 +2365,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de dolor menstrual en 2012</t>
+          <t>Población con diagnóstico de dolor menstrual en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3190,7 +2387,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3199,17 +2396,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -3280,41 +2466,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -3337,13 +2488,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -3358,37 +2502,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14311</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22959</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +2547,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7870</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22878</t>
+          <t>22959</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,47 +2562,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>14311</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>7870</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>22878</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>7,28%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -3471,37 +2580,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>269</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>300143</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>291495</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>306368</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +2625,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>291576</t>
+          <t>291495</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>306584</t>
+          <t>306368</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,47 +2640,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>300143</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>291576</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>306584</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>95,45%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>92,72%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>97,5%</t>
+          <t>97,43%</t>
         </is>
       </c>
     </row>
@@ -3584,37 +2658,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>283</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>314454</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>314454</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>314454</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3648,41 +2722,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>314454</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>314454</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>314454</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3701,37 +2740,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16722</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10091</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>25438</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +2785,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>10091</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24690</t>
+          <t>25438</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,47 +2800,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>16722</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>9939</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>24690</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>2,94%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>7,3%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -3814,37 +2818,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>288</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>321289</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>312573</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>327920</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +2863,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>313321</t>
+          <t>312573</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>328072</t>
+          <t>327920</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,47 +2878,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>321289</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>313321</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>328072</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>95,05%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>92,7%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>97,06%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -3927,37 +2896,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>305</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>338011</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>338011</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>338011</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3991,41 +2960,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>338011</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>338011</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>338011</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4044,37 +2978,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9075</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17904</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +3023,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4135</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18324</t>
+          <t>17904</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,47 +3038,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>9075</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>4135</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>18324</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>7,04%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -4157,37 +3056,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>236</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>251054</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>242225</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>256084</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +3101,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>241805</t>
+          <t>242225</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>255994</t>
+          <t>256084</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,47 +3116,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>251054</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>241805</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>255994</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>96,51%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>92,96%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>98,41%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -4270,37 +3134,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>244</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>260129</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>260129</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>260129</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4334,41 +3198,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>260129</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>260129</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>260129</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4387,37 +3216,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>37156</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26278</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>50284</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +3261,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26681</t>
+          <t>26278</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51235</t>
+          <t>50284</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,47 +3276,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>37156</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>26681</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>51235</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>4,86%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>6,7%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -4500,37 +3294,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>674</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>727566</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>714438</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>738444</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +3339,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>713487</t>
+          <t>714438</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>738041</t>
+          <t>738444</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,47 +3354,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>674</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>727566</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>713487</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>738041</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>95,14%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>93,3%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>96,51%</t>
+          <t>96,56%</t>
         </is>
       </c>
     </row>
@@ -4613,37 +3372,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>710</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>764722</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>764722</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>764722</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4677,41 +3436,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>710</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>764722</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>764722</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>764722</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4730,37 +3454,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21793</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13659</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>32477</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +3499,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13898</t>
+          <t>13659</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32661</t>
+          <t>32477</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,47 +3514,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>21793</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>13898</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>32661</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>4,3%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -4843,37 +3532,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>681</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>738453</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>727769</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>746587</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +3577,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>727585</t>
+          <t>727769</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>746348</t>
+          <t>746587</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,47 +3592,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>681</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>738453</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>727585</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>746348</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>97,13%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>95,7%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>98,17%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -4956,37 +3610,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>702</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>760246</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>760246</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>760246</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5020,41 +3674,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>702</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>760246</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>760246</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>760246</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5073,37 +3692,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>38353</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26381</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>51945</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +3737,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26295</t>
+          <t>26381</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51916</t>
+          <t>51945</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,45 +3752,10 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>38353</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>26295</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>51916</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
         <is>
           <t>4,68%</t>
         </is>
@@ -5186,37 +3770,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1070998</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1057406</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1082970</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +3815,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1057435</t>
+          <t>1057406</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1083056</t>
+          <t>1082970</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5251,42 +3835,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1007</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1070998</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>1057435</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>1083056</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>96,54%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>95,32%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>97,63%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -5299,37 +3848,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1109351</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1109351</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1109351</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5363,41 +3912,6 @@
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>1044</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>1109351</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>1109351</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>1109351</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5416,37 +3930,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>133</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>137409</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>113834</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>162706</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +3975,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>117922</t>
+          <t>113834</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>163004</t>
+          <t>162706</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,47 +3990,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>137409</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>117922</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>163004</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>3,87%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>3,32%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>4,6%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -5529,37 +4008,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3155</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3409506</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3384209</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3433081</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +4053,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3383911</t>
+          <t>3384209</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3428993</t>
+          <t>3433081</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,47 +4068,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>3155</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>3409506</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>3383911</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>3428993</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>96,13%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>95,4%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>96,68%</t>
+          <t>96,79%</t>
         </is>
       </c>
     </row>
@@ -5642,37 +4086,37 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3288</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3546915</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3546915</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3546915</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5706,41 +4150,6 @@
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>3288</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>3546915</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>3546915</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>3546915</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5754,7 +4163,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -5762,7 +4171,6 @@
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
@@ -5777,7 +4185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5796,25 +4204,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de dolor menstrual en 2016</t>
+          <t>Población con diagnóstico de dolor menstrual en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5825,7 +4226,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5834,17 +4235,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -5915,41 +4305,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -5972,13 +4327,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -5993,37 +4341,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11977</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6747</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20602</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +4386,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6177</t>
+          <t>6747</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19828</t>
+          <t>20602</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,47 +4401,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>11977</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>6177</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>19828</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>3,45%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>5,71%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -6106,37 +4419,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>320</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>335078</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>326453</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>340308</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +4464,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>327227</t>
+          <t>326453</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>340878</t>
+          <t>340308</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,47 +4479,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>335078</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>327227</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>340878</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>96,55%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>94,29%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>98,22%</t>
+          <t>98,06%</t>
         </is>
       </c>
     </row>
@@ -6219,37 +4497,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>332</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>347055</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>347055</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>347055</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6283,41 +4561,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>347055</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>347055</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>347055</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6336,37 +4579,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13772</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7862</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22956</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +4624,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7838</t>
+          <t>7862</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22503</t>
+          <t>22956</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6401,42 +4644,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>13772</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>7838</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>22503</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>6,04%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -6449,37 +4657,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>338</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>358501</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>349317</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>364411</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +4702,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>349770</t>
+          <t>349317</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>364435</t>
+          <t>364411</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,45 +4717,10 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>97,89%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>358501</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>349770</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>364435</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>96,3%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>93,96%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
         <is>
           <t>97,89%</t>
         </is>
@@ -6562,37 +4735,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>352</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>372273</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>372273</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>372273</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6626,41 +4799,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>352</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>372273</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>372273</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>372273</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6679,37 +4817,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9676</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +4862,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10394</t>
+          <t>9676</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,47 +4877,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>3953</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>1020</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>10394</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>6,26%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -6792,37 +4895,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>149</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>162170</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>156447</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>165123</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +4940,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155729</t>
+          <t>156447</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165103</t>
+          <t>165123</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,47 +4955,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>162170</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>155729</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>165103</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>97,62%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>93,74%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>99,39%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -6905,37 +4973,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>153</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>166123</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>166123</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>166123</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6969,41 +5037,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>166123</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>166123</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>166123</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7022,37 +5055,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9502</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4755</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17191</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +5100,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>4755</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16583</t>
+          <t>17191</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,47 +5115,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>9502</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>4631</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>16583</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -7135,37 +5133,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>788</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>816374</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>808685</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>821121</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +5178,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>809293</t>
+          <t>808685</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>821245</t>
+          <t>821121</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,47 +5193,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>788</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>816374</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>809293</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>821245</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>98,85%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>97,99%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>99,44%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -7248,37 +5211,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>798</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>825876</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>825876</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>825876</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7312,41 +5275,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>798</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>825876</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>825876</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>825876</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7365,37 +5293,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15666</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9161</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24940</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +5338,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8743</t>
+          <t>9161</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24672</t>
+          <t>24940</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,47 +5353,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>15666</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>8743</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>24672</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>3,34%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -7478,37 +5371,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>683</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>722578</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>713304</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>729083</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +5416,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>713572</t>
+          <t>713304</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>729501</t>
+          <t>729083</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,47 +5431,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>722578</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>713572</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>729501</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>97,88%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>96,66%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>98,82%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -7591,37 +5449,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>699</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>738244</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>738244</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>738244</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7655,41 +5513,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>699</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>738244</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>738244</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>738244</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7708,37 +5531,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11519</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5914</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19324</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +5576,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>5914</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19936</t>
+          <t>19324</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7773,42 +5596,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>11519</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>5988</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>19936</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -7821,37 +5609,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>981</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1070506</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1062701</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1076111</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +5654,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1062089</t>
+          <t>1062701</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1076037</t>
+          <t>1076111</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,45 +5669,10 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>981</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1070506</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>1062089</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>1076037</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>98,94%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>98,16%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
         <is>
           <t>99,45%</t>
         </is>
@@ -7934,37 +5687,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>992</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1082025</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1082025</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1082025</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7998,41 +5751,6 @@
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>992</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>1082025</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>1082025</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>1082025</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8051,37 +5769,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>67</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>66388</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>51849</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>85345</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +5814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>52765</t>
+          <t>51849</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>84233</t>
+          <t>85345</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,47 +5829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>66388</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>52765</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>84233</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -8164,37 +5847,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3259</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3465208</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3446251</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3479747</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +5892,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3447363</t>
+          <t>3446251</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3478831</t>
+          <t>3479747</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,47 +5907,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>3259</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>3465208</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>3447363</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>3478831</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>98,12%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>97,61%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>98,51%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -8277,37 +5925,37 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3531596</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3531596</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3531596</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8341,41 +5989,6 @@
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>3326</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>3531596</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>3531596</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>3531596</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8389,7 +6002,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -8397,7 +6010,6 @@
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
@@ -8412,7 +6024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8431,25 +6043,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de dolor menstrual en 2023</t>
+          <t>Población con diagnóstico de dolor menstrual en 2023 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -8460,7 +6065,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -8469,17 +6074,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -8550,41 +6144,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -8607,13 +6166,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -8628,37 +6180,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>40498</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>30116</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>52926</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +6225,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29497</t>
+          <t>30116</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53283</t>
+          <t>52926</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,47 +6240,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>40498</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>29497</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>53283</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>9,08%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>6,61%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>11,95%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -8741,37 +6258,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>635</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>405457</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>393029</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>415839</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +6303,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>392672</t>
+          <t>393029</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>416458</t>
+          <t>415839</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,47 +6318,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>635</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>405457</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>392672</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>416458</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>90,92%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>88,05%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>93,39%</t>
+          <t>93,25%</t>
         </is>
       </c>
     </row>
@@ -8854,37 +6336,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>684</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>445955</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>445955</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>445955</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8918,41 +6400,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>684</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>445955</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>445955</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>445955</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8971,37 +6418,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>29322</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21051</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>39976</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +6463,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21646</t>
+          <t>21051</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40127</t>
+          <t>39976</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,47 +6478,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>29322</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>21646</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>40127</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>7,7%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>5,69%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>10,54%</t>
+          <t>10,5%</t>
         </is>
       </c>
     </row>
@@ -9084,37 +6496,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>547</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>351288</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>340634</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>359559</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +6541,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>340483</t>
+          <t>340634</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>358964</t>
+          <t>359559</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,47 +6556,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>351288</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>340483</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>358964</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>92,3%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>89,46%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>94,31%</t>
+          <t>94,47%</t>
         </is>
       </c>
     </row>
@@ -9197,37 +6574,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>587</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>380610</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>380610</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>380610</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9261,41 +6638,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>380610</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>380610</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>380610</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9314,37 +6656,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6647</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3047</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13834</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +6701,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2736</t>
+          <t>3047</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12709</t>
+          <t>13834</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,47 +6716,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>6647</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>2736</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>12709</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>7,61%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -9427,37 +6734,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>279</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>160264</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>153077</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>163864</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +6779,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>154202</t>
+          <t>153077</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>164175</t>
+          <t>163864</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,47 +6794,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>160264</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>154202</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>164175</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>96,02%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>92,39%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>98,36%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -9540,37 +6812,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>289</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>166911</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>166911</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>166911</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9604,41 +6876,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>166911</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>166911</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>166911</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9657,37 +6894,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>57834</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>27440</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>79109</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +6939,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25247</t>
+          <t>27440</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>78289</t>
+          <t>79109</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,47 +6954,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>57834</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>25247</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>78289</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>5,93%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>8,03%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -9770,37 +6972,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>917540</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>896265</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>947934</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +7017,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>897085</t>
+          <t>896265</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>950127</t>
+          <t>947934</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,47 +7032,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1148</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>917540</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>897085</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>950127</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>94,07%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>91,97%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>97,41%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -9883,37 +7050,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>975374</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>975374</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>975374</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9947,41 +7114,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>1226</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>975374</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>975374</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>975374</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10000,37 +7132,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>56</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>105493</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>35685</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>300223</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +7177,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35578</t>
+          <t>35685</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>300040</t>
+          <t>300223</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,47 +7192,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>105493</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>35578</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>300040</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>12,6%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>35,83%</t>
+          <t>35,85%</t>
         </is>
       </c>
     </row>
@@ -10113,37 +7210,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>732013</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>537283</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>801821</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +7255,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>537466</t>
+          <t>537283</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>801928</t>
+          <t>801821</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,47 +7270,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1231</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>732013</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>537466</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>801928</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>87,4%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>64,17%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>95,75%</t>
+          <t>95,74%</t>
         </is>
       </c>
     </row>
@@ -10226,37 +7288,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>837506</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>837506</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>837506</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10290,41 +7352,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>1287</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>837506</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>837506</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>837506</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10343,37 +7370,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23685</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13391</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>40504</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +7415,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13634</t>
+          <t>13391</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>38550</t>
+          <t>40504</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,47 +7430,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>23685</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>13634</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>38550</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>3,11%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>5,07%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -10456,37 +7448,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>737007</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>720188</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>747301</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +7493,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>722142</t>
+          <t>720188</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>747058</t>
+          <t>747301</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,47 +7508,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>737007</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>722142</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>747058</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>96,89%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>94,93%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>98,21%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -10569,37 +7526,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>760692</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>760692</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>760692</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10633,41 +7590,6 @@
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>1158</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>760692</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>760692</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>760692</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10686,37 +7608,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>249</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>263480</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>188120</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>555773</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +7653,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>185125</t>
+          <t>188120</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>480818</t>
+          <t>555773</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,47 +7668,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>263480</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>185125</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>480818</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>7,39%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>5,19%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>13,48%</t>
+          <t>15,58%</t>
         </is>
       </c>
     </row>
@@ -10799,37 +7686,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4982</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3303567</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3011274</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3378927</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +7731,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3086229</t>
+          <t>3011274</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3381922</t>
+          <t>3378927</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,47 +7746,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>4982</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>3303567</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>3086229</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>3381922</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>92,61%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>86,52%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>94,81%</t>
+          <t>94,73%</t>
         </is>
       </c>
     </row>
@@ -10912,37 +7764,37 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5231</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3567047</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3567047</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3567047</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10976,41 +7828,6 @@
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>5231</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>3567047</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>3567047</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>3567047</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -11024,7 +7841,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -11032,7 +7849,6 @@
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>

--- a/data/trans_orig/P1435-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1435-Clase-trans_orig.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14384</t>
+          <t>14467</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32019</t>
+          <t>32140</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14384</t>
+          <t>14467</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32019</t>
+          <t>32140</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,48%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>274661</t>
+          <t>274540</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>292296</t>
+          <t>292213</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>274661</t>
+          <t>274540</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>292296</t>
+          <t>292213</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,28%</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38199</t>
+          <t>37345</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63879</t>
+          <t>65108</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38199</t>
+          <t>37345</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63879</t>
+          <t>65108</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,51%</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>307986</t>
+          <t>306757</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>333666</t>
+          <t>334520</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>307986</t>
+          <t>306757</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>333666</t>
+          <t>334520</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,96%</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9266</t>
+          <t>8937</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25028</t>
+          <t>24229</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9266</t>
+          <t>8937</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25028</t>
+          <t>24229</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>142754</t>
+          <t>143553</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>158516</t>
+          <t>158845</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>142754</t>
+          <t>143553</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158516</t>
+          <t>158845</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1277,12 +1277,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,67%</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54519</t>
+          <t>54524</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85252</t>
+          <t>85060</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54519</t>
+          <t>54524</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85252</t>
+          <t>85060</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>629033</t>
+          <t>629225</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>659766</t>
+          <t>659761</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>629033</t>
+          <t>629225</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>659766</t>
+          <t>659761</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18567</t>
+          <t>17970</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39060</t>
+          <t>39585</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18567</t>
+          <t>17970</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39060</t>
+          <t>39585</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -1703,12 +1703,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>529692</t>
+          <t>529167</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>550185</t>
+          <t>550782</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1718,12 +1718,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>529692</t>
+          <t>529167</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>550185</t>
+          <t>550782</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,84%</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1863,12 +1863,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>62330</t>
+          <t>60992</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>93823</t>
+          <t>92668</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>62330</t>
+          <t>60992</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>93823</t>
+          <t>92668</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1913,12 +1913,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -1941,12 +1941,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1154937</t>
+          <t>1156092</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1186430</t>
+          <t>1187768</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1154937</t>
+          <t>1156092</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1186430</t>
+          <t>1187768</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1991,12 +1991,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,12%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>234102</t>
+          <t>233670</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>292170</t>
+          <t>291268</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>234102</t>
+          <t>233670</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>292170</t>
+          <t>291268</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -2179,12 +2179,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3085954</t>
+          <t>3086856</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3144022</t>
+          <t>3144454</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2194,12 +2194,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3085954</t>
+          <t>3086856</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3144022</t>
+          <t>3144454</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,08%</t>
         </is>
       </c>
     </row>
@@ -2512,12 +2512,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>7876</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22959</t>
+          <t>23023</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2527,12 +2527,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2547,12 +2547,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>7876</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22959</t>
+          <t>23023</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -2590,12 +2590,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>291495</t>
+          <t>291431</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>306368</t>
+          <t>306578</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2625,12 +2625,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>291495</t>
+          <t>291431</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>306368</t>
+          <t>306578</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -2750,12 +2750,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10091</t>
+          <t>10296</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25438</t>
+          <t>25611</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2785,12 +2785,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10091</t>
+          <t>10296</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25438</t>
+          <t>25611</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2800,12 +2800,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -2828,12 +2828,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>312573</t>
+          <t>312400</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>327920</t>
+          <t>327715</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>312573</t>
+          <t>312400</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>327920</t>
+          <t>327715</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -2988,12 +2988,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4045</t>
+          <t>4059</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17904</t>
+          <t>16924</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3003,12 +3003,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4045</t>
+          <t>4059</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17904</t>
+          <t>16924</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -3066,12 +3066,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>242225</t>
+          <t>243205</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>256084</t>
+          <t>256070</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>242225</t>
+          <t>243205</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>256084</t>
+          <t>256070</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,44%</t>
         </is>
       </c>
     </row>
@@ -3226,12 +3226,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26278</t>
+          <t>27147</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50284</t>
+          <t>50642</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26278</t>
+          <t>27147</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50284</t>
+          <t>50642</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -3304,12 +3304,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>714438</t>
+          <t>714080</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>738444</t>
+          <t>737575</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3339,12 +3339,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>714438</t>
+          <t>714080</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>738444</t>
+          <t>737575</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3354,12 +3354,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,45%</t>
         </is>
       </c>
     </row>
@@ -3464,12 +3464,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13659</t>
+          <t>13713</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32477</t>
+          <t>32996</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13659</t>
+          <t>13713</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32477</t>
+          <t>32996</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -3542,12 +3542,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>727769</t>
+          <t>727250</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>746587</t>
+          <t>746533</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -3577,12 +3577,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>727769</t>
+          <t>727250</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>746587</t>
+          <t>746533</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -3682,7 +3682,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26381</t>
+          <t>26990</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>51945</t>
+          <t>52321</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -3717,12 +3717,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26381</t>
+          <t>26990</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51945</t>
+          <t>52321</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -3752,12 +3752,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -3780,12 +3780,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1057406</t>
+          <t>1057030</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1082970</t>
+          <t>1082361</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1057406</t>
+          <t>1057030</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1082970</t>
+          <t>1082361</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -3830,12 +3830,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -3940,12 +3940,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>113834</t>
+          <t>115409</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>162706</t>
+          <t>162708</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>113834</t>
+          <t>115409</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>162706</t>
+          <t>162708</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -4018,12 +4018,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3384209</t>
+          <t>3384207</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3433081</t>
+          <t>3431506</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3384209</t>
+          <t>3384207</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3433081</t>
+          <t>3431506</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,75%</t>
         </is>
       </c>
     </row>
@@ -4351,12 +4351,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6747</t>
+          <t>5888</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20602</t>
+          <t>20101</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4386,12 +4386,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6747</t>
+          <t>5888</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20602</t>
+          <t>20101</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -4429,12 +4429,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>326453</t>
+          <t>326954</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>340308</t>
+          <t>341167</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>326453</t>
+          <t>326954</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>340308</t>
+          <t>341167</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,3%</t>
         </is>
       </c>
     </row>
@@ -4589,12 +4589,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7862</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22956</t>
+          <t>22270</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4604,12 +4604,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4624,12 +4624,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7862</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22956</t>
+          <t>22270</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -4667,12 +4667,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>349317</t>
+          <t>350003</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>364411</t>
+          <t>364581</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>349317</t>
+          <t>350003</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>364411</t>
+          <t>364581</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4717,12 +4717,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9676</t>
+          <t>9277</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9676</t>
+          <t>9277</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -4905,12 +4905,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>156447</t>
+          <t>156846</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>165123</t>
+          <t>165094</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4920,12 +4920,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>156447</t>
+          <t>156846</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165123</t>
+          <t>165094</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4955,12 +4955,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -5065,12 +5065,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17191</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5080,12 +5080,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17191</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -5143,12 +5143,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>808685</t>
+          <t>809548</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>821121</t>
+          <t>821951</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>808685</t>
+          <t>809548</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>821121</t>
+          <t>821951</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5193,12 +5193,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -5303,12 +5303,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9161</t>
+          <t>9310</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24940</t>
+          <t>23338</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9161</t>
+          <t>9310</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24940</t>
+          <t>23338</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -5381,12 +5381,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>713304</t>
+          <t>714906</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>729083</t>
+          <t>728934</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5396,12 +5396,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>713304</t>
+          <t>714906</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>729083</t>
+          <t>728934</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5521,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5914</t>
+          <t>5919</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19324</t>
+          <t>20291</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5914</t>
+          <t>5919</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19324</t>
+          <t>20291</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1062701</t>
+          <t>1061734</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1076111</t>
+          <t>1076106</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1062701</t>
+          <t>1061734</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1076111</t>
+          <t>1076106</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5779,12 +5779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>51849</t>
+          <t>51846</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>85345</t>
+          <t>84151</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>51849</t>
+          <t>51846</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>85345</t>
+          <t>84151</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -5857,12 +5857,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3446251</t>
+          <t>3447445</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3479747</t>
+          <t>3479750</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3446251</t>
+          <t>3447445</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3479747</t>
+          <t>3479750</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6185,32 +6185,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>40498</t>
+          <t>42805</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30116</t>
+          <t>31443</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52926</t>
+          <t>56044</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6220,32 +6220,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>40498</t>
+          <t>42805</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30116</t>
+          <t>31443</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52926</t>
+          <t>56044</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,51%</t>
         </is>
       </c>
     </row>
@@ -6263,32 +6263,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>405457</t>
+          <t>444058</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>393029</t>
+          <t>430819</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>415839</t>
+          <t>455420</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6298,32 +6298,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>405457</t>
+          <t>444058</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>393029</t>
+          <t>430819</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>415839</t>
+          <t>455420</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,54%</t>
         </is>
       </c>
     </row>
@@ -6341,17 +6341,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>445955</t>
+          <t>486863</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>445955</t>
+          <t>486863</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>445955</t>
+          <t>486863</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6376,17 +6376,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>445955</t>
+          <t>486863</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>445955</t>
+          <t>486863</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>445955</t>
+          <t>486863</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6423,32 +6423,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29322</t>
+          <t>32650</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21051</t>
+          <t>24119</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39976</t>
+          <t>44734</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6458,32 +6458,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29322</t>
+          <t>32650</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21051</t>
+          <t>24119</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39976</t>
+          <t>44734</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -6501,32 +6501,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>351288</t>
+          <t>388444</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>340634</t>
+          <t>376360</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>359559</t>
+          <t>396975</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6536,32 +6536,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>351288</t>
+          <t>388444</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>340634</t>
+          <t>376360</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>359559</t>
+          <t>396975</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,27%</t>
         </is>
       </c>
     </row>
@@ -6579,17 +6579,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>380610</t>
+          <t>421094</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>380610</t>
+          <t>421094</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>380610</t>
+          <t>421094</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6614,17 +6614,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>380610</t>
+          <t>421094</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>380610</t>
+          <t>421094</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>380610</t>
+          <t>421094</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6661,32 +6661,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6647</t>
+          <t>8766</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>4203</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13834</t>
+          <t>15754</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6696,32 +6696,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6647</t>
+          <t>8766</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>4203</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13834</t>
+          <t>15754</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -6739,32 +6739,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>160264</t>
+          <t>178731</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>153077</t>
+          <t>171743</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>163864</t>
+          <t>183294</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6774,32 +6774,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>160264</t>
+          <t>178731</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>153077</t>
+          <t>171743</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>163864</t>
+          <t>183294</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>97,76%</t>
         </is>
       </c>
     </row>
@@ -6817,17 +6817,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6852,17 +6852,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6899,32 +6899,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>57834</t>
+          <t>67143</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27440</t>
+          <t>53238</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>79109</t>
+          <t>84895</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6934,32 +6934,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>57834</t>
+          <t>67143</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27440</t>
+          <t>53238</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79109</t>
+          <t>84895</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -6977,32 +6977,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>917540</t>
+          <t>790062</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>896265</t>
+          <t>772310</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>947934</t>
+          <t>803967</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7012,32 +7012,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>917540</t>
+          <t>790062</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>896265</t>
+          <t>772310</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>947934</t>
+          <t>803967</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>93,79%</t>
         </is>
       </c>
     </row>
@@ -7055,17 +7055,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>975374</t>
+          <t>857205</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>975374</t>
+          <t>857205</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>975374</t>
+          <t>857205</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7090,17 +7090,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>975374</t>
+          <t>857205</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>975374</t>
+          <t>857205</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>975374</t>
+          <t>857205</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7137,32 +7137,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>105493</t>
+          <t>42222</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35685</t>
+          <t>32203</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>300223</t>
+          <t>54825</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7172,32 +7172,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>105493</t>
+          <t>42222</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35685</t>
+          <t>32203</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>300223</t>
+          <t>54825</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -7215,32 +7215,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>732013</t>
+          <t>786391</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>537283</t>
+          <t>773788</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>801821</t>
+          <t>796410</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7250,32 +7250,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>732013</t>
+          <t>786391</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>537283</t>
+          <t>773788</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>801821</t>
+          <t>796410</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>96,11%</t>
         </is>
       </c>
     </row>
@@ -7293,17 +7293,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>837506</t>
+          <t>828613</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>837506</t>
+          <t>828613</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>837506</t>
+          <t>828613</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7328,17 +7328,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>837506</t>
+          <t>828613</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>837506</t>
+          <t>828613</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>837506</t>
+          <t>828613</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7360,7 +7360,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7375,32 +7375,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>23685</t>
+          <t>26937</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13391</t>
+          <t>15296</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40504</t>
+          <t>43618</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7410,32 +7410,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>23685</t>
+          <t>26937</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13391</t>
+          <t>15296</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40504</t>
+          <t>43618</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -7453,32 +7453,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>737007</t>
+          <t>816659</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>720188</t>
+          <t>799978</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>747301</t>
+          <t>828300</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7488,32 +7488,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>737007</t>
+          <t>816659</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>720188</t>
+          <t>799978</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>747301</t>
+          <t>828300</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -7531,17 +7531,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>760692</t>
+          <t>843596</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>760692</t>
+          <t>843596</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>760692</t>
+          <t>843596</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7566,17 +7566,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760692</t>
+          <t>843596</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760692</t>
+          <t>843596</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760692</t>
+          <t>843596</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7613,32 +7613,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>263480</t>
+          <t>220523</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>188120</t>
+          <t>191780</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>555773</t>
+          <t>252976</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7648,32 +7648,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>263480</t>
+          <t>220523</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>188120</t>
+          <t>191780</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>555773</t>
+          <t>252976</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -7691,32 +7691,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3303567</t>
+          <t>3404345</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3011274</t>
+          <t>3371892</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3378927</t>
+          <t>3433088</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7726,32 +7726,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3303567</t>
+          <t>3404345</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3011274</t>
+          <t>3371892</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3378927</t>
+          <t>3433088</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,71%</t>
         </is>
       </c>
     </row>
@@ -7769,17 +7769,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3567047</t>
+          <t>3624868</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3567047</t>
+          <t>3624868</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3567047</t>
+          <t>3624868</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7804,17 +7804,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3567047</t>
+          <t>3624868</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3567047</t>
+          <t>3624868</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3567047</t>
+          <t>3624868</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
